--- a/KURIKULUM2026_REVISI/015_SIMULASI_AKSELERASI_KELULUSAN_7_SEMESTER.xlsx
+++ b/KURIKULUM2026_REVISI/015_SIMULASI_AKSELERASI_KELULUSAN_7_SEMESTER.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>`STI-201`</t>
+          <t>`STI-204`</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>`STI-202`</t>
+          <t>`STI-205`</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>`STI-301`</t>
+          <t>`STI-306`</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>`STI-302`</t>
+          <t>`STI-307`</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>`FST-204` AI Dasar, `STI-201` Matdis</t>
+          <t>`FST-204` AI Dasar, `STI-204` Matdis</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>`STI-303`</t>
+          <t>`STI-308`</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>`STI-304`</t>
+          <t>`STI-309`</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>`STI-305`</t>
+          <t>`STI-310`</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>`STI-306`</t>
+          <t>`STI-311`</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>`STI-307`</t>
+          <t>`STI-312`</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>**`STI-506`**</t>
+          <t>**`STI-523`**</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>`STI-401`</t>
+          <t>`STI-413`</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>`STI-202` Aljabar, `STI-302` Sistem Cerdas</t>
+          <t>`STI-205` Aljabar, `STI-307` Sistem Cerdas</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>`STI-403`</t>
+          <t>`STI-414`</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>`STI-302` Sistem Cerdas</t>
+          <t>`STI-307` Sistem Cerdas</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>`STI-402`</t>
+          <t>`STI-415`</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>`STI-407`</t>
+          <t>`STI-416`</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>`FST-207` Basis Data, `STI-306` Front End</t>
+          <t>`FST-207` Basis Data, `STI-311` Front End</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>`STI-307` Jarkom, `STI-305` OS</t>
+          <t>`STI-312` Jarkom, `STI-310` OS</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>`STI-307` Jaringan Komputer</t>
+          <t>`STI-312` Jaringan Komputer</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>**`STI-602`**</t>
+          <t>**`STI-625`**</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>`STI-501`</t>
+          <t>`STI-519`</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>`STI-401` Machine Learning</t>
+          <t>`STI-413` Machine Learning</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>`STI-503`</t>
+          <t>`STI-520`</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>`STI-401` ML, `STI-402` DW/BI</t>
+          <t>`STI-413` ML, `STI-415` DW/BI</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>`STI-504`</t>
+          <t>`STI-521`</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>`STI-307` Jarkom, `STI-305` OS</t>
+          <t>`STI-312` Jarkom, `STI-310` OS</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>`STI-505`</t>
+          <t>`STI-522`</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>`STI-306` Front, `STI-407` Back End</t>
+          <t>`STI-311` Front, `STI-416` Back End</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>**`STI-701`**</t>
+          <t>**`STI-728`**</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>`STI-601`</t>
+          <t>`STI-624`</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>`STI-501` Deep Learning, `STI-407` Back End</t>
+          <t>`STI-626` Deep Learning, `STI-416` Back End</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>`STI-603`</t>
+          <t>`STI-626`</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>`STI-405` Dasar Keamanan Informasi</t>
+          <t>`STI-418` Dasar Keamanan Informasi</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>`STI-604`</t>
+          <t>`STI-627`</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>`STI-407` Web Back End Development</t>
+          <t>`STI-416` Web Back End Development</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>**Akselerasi: STI-506 Manpro Selesai, Syarat $\ge 100\text{ SKS}$ Terpenuhi ✅**</t>
+          <t>**Akselerasi: STI-523 Manpro Selesai, Syarat $\ge 100\text{ SKS}$ Terpenuhi ✅**</t>
         </is>
       </c>
     </row>
